--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488205_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488205_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4608</v>
+        <v>5.6079</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6668</v>
+        <v>2.528</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7939</v>
+        <v>3.0799</v>
       </c>
       <c r="G2" t="n">
         <v>6.8572</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>0.142</v>
+        <v>0.2891</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4562</v>
+        <v>-0.595</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5981</v>
+        <v>0.8841</v>
       </c>
       <c r="V2" t="n">
         <v>0.3144</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>J. SOSA LLANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7211</v>
+        <v>2.3321</v>
       </c>
       <c r="E3" t="n">
-        <v>0.962</v>
+        <v>0.9788</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7591</v>
+        <v>1.3533</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3744</v>
+        <v>1.5305</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0127</v>
+        <v>0.1143</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3872</v>
+        <v>1.4162</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2173</v>
+        <v>1.3071</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1758</v>
+        <v>0.0215</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0415</v>
+        <v>1.2856</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1572</v>
+        <v>0.2234</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1885</v>
+        <v>0.0929</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3457</v>
+        <v>0.1306</v>
       </c>
       <c r="P3" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8458</v>
+        <v>-0.3843</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6156</v>
+        <v>-0.3283</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2303</v>
+        <v>-0.056</v>
       </c>
       <c r="V3" t="n">
-        <v>0.945</v>
+        <v>0.63</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SOSA LLANO</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.209</v>
+        <v>2.1733</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9788</v>
+        <v>-0.4114</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2302</v>
+        <v>2.5847</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5305</v>
+        <v>0.161</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1143</v>
+        <v>1.6063</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4162</v>
+        <v>-1.4453</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3071</v>
+        <v>-0.2868</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0215</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2856</v>
+        <v>-1.2228</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2234</v>
+        <v>0.4477</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0929</v>
+        <v>0.6703</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1306</v>
+        <v>-0.2226</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5074</v>
+        <v>0.1589</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3283</v>
+        <v>-0.1246</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1791</v>
+        <v>0.2835</v>
       </c>
       <c r="V4" t="n">
-        <v>0.63</v>
+        <v>0.0005</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.63</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9604</v>
+        <v>1.9234</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6735</v>
+        <v>0.3859</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6339</v>
+        <v>1.5375</v>
       </c>
       <c r="G5" t="n">
-        <v>0.161</v>
+        <v>0.3744</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6063</v>
+        <v>-0.0127</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4453</v>
+        <v>0.3872</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2868</v>
+        <v>0.2173</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.1758</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2228</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4477</v>
+        <v>0.1572</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6703</v>
+        <v>-0.1885</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2226</v>
+        <v>0.3457</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.054</v>
+        <v>0.0482</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3867</v>
+        <v>0.0395</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3327</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0005</v>
+        <v>0.945</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0005</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.5204</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.014</v>
+        <v>-1.0156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6102</v>
+        <v>1.536</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3643</v>
+        <v>0.9482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.633</v>
+        <v>0.5705</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7313</v>
+        <v>0.3778</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2913</v>
+        <v>0.3065</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1668</v>
+        <v>0.9273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1244</v>
+        <v>-0.6208</v>
       </c>
       <c r="M6" t="n">
-        <v>0.073</v>
+        <v>0.6418</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3568</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6069</v>
+        <v>0.9986</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3808</v>
+        <v>-0.2801</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0621</v>
+        <v>-0.3771</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4429</v>
+        <v>0.097</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.8899</v>
+        <v>-1.2594</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3166</v>
+        <v>-0.945</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5733</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1657</v>
+        <v>0.2817</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3324</v>
+        <v>-0.23</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1667</v>
+        <v>0.5118</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9482</v>
+        <v>1.3643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5705</v>
+        <v>0.633</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3778</v>
+        <v>0.7313</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3065</v>
+        <v>1.2913</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9273</v>
+        <v>1.1668</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6208</v>
+        <v>0.1244</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6418</v>
+        <v>0.073</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3568</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9986</v>
+        <v>0.6069</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9661999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6939</v>
+        <v>-0.2782</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2724</v>
+        <v>0.3444</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2594</v>
+        <v>-1.8899</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.945</v>
+        <v>-0.3166</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3144</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3923</v>
+        <v>0.012</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0593</v>
+        <v>-0.8519</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6669</v>
+        <v>0.8639</v>
       </c>
       <c r="G8" t="n">
         <v>0.5669</v>
@@ -1078,13 +1078,13 @@
         <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1446</v>
+        <v>-0.7402</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.766</v>
+        <v>-0.5586</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3785</v>
+        <v>-0.1816</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0519</v>
+        <v>-0.3904</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.758</v>
+        <v>-2.4412</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7061</v>
+        <v>2.0508</v>
       </c>
       <c r="G9" t="n">
         <v>0.2452</v>
@@ -1156,13 +1156,13 @@
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7973</v>
+        <v>-0.1359</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6392</v>
+        <v>-0.3224</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1582</v>
+        <v>0.1865</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.099</v>
+        <v>-0.9458</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4221</v>
+        <v>-1.3674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3231</v>
+        <v>0.4216</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3922</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6332</v>
+        <v>-0.48</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7113</v>
+        <v>-0.6566</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0781</v>
+        <v>0.1766</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>M. JIMENEZ CUEVAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3049</v>
+        <v>-1.1276</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.325</v>
+        <v>-1.5279</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0201</v>
+        <v>0.4002</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1829</v>
+        <v>-0.8276</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4114</v>
+        <v>-0.4544</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5944</v>
+        <v>-0.3732</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1314</v>
+        <v>-0.5899</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1329</v>
+        <v>-0.6314</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2643</v>
+        <v>0.0415</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0515</v>
+        <v>-0.2377</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2786</v>
+        <v>0.177</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3301</v>
+        <v>-0.4147</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1117</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7513</v>
+        <v>0.0706</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7113</v>
+        <v>-0.0115</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0401</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JIMENEZ CUEVAS</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3295</v>
+        <v>-1.1517</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6805</v>
+        <v>-2.2703</v>
       </c>
       <c r="F12" t="n">
-        <v>0.351</v>
+        <v>1.1186</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8276</v>
+        <v>-1.1829</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4544</v>
+        <v>0.4114</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3732</v>
+        <v>-1.5944</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5899</v>
+        <v>-1.1314</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6314</v>
+        <v>0.1329</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0415</v>
+        <v>-1.2643</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2377</v>
+        <v>-0.0515</v>
       </c>
       <c r="N12" t="n">
-        <v>0.177</v>
+        <v>0.2786</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4147</v>
+        <v>-0.3301</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>-1.1117</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1313</v>
+        <v>-0.5981</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1641</v>
+        <v>-0.6566</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0328</v>
+        <v>0.0584</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8872</v>
+        <v>-1.8768</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4851</v>
+        <v>-3.2777</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5979</v>
+        <v>1.4009</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2014</v>
@@ -1468,13 +1468,13 @@
         <v>1.297</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.574</v>
+        <v>-0.5636</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9637</v>
+        <v>-0.7564</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3897</v>
+        <v>0.1927</v>
       </c>
       <c r="V13" t="n">
         <v>0.6294</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.717099999999999</v>
+        <v>7.3585</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.1423</v>
+        <v>-9.5007</v>
       </c>
       <c r="F14" t="n">
-        <v>16.8591</v>
+        <v>16.8592</v>
       </c>
       <c r="G14" t="n">
         <v>7.443599999999998</v>
@@ -1516,16 +1516,16 @@
         <v>6.9057</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5379999999999998</v>
+        <v>0.5380000000000003</v>
       </c>
       <c r="J14" t="n">
-        <v>5.913400000000002</v>
+        <v>5.913400000000001</v>
       </c>
       <c r="K14" t="n">
         <v>6.644100000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7308</v>
+        <v>-0.7307999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>1.5304</v>
@@ -1546,13 +1546,13 @@
         <v>14.823</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.1907</v>
+        <v>-2.5492</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.267200000000001</v>
+        <v>-4.6258</v>
       </c>
       <c r="U14" t="n">
-        <v>2.0763</v>
+        <v>2.0764</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3150000000000004</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4154</v>
+        <v>2.7108</v>
       </c>
       <c r="E15" t="n">
         <v>0.944</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4714</v>
+        <v>1.7669</v>
       </c>
       <c r="G15" t="n">
         <v>2.2331</v>
@@ -1624,13 +1624,13 @@
         <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0766</v>
+        <v>0.2189</v>
       </c>
       <c r="T15" t="n">
         <v>-0.383</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3064</v>
+        <v>0.6019</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5195</v>
+        <v>1.0791</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6204</v>
+        <v>0.1307</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8991</v>
+        <v>0.9484</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2178</v>
@@ -1702,13 +1702,13 @@
         <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>0.922</v>
+        <v>0.4816</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6367</v>
+        <v>0.1471</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2853</v>
+        <v>0.3345</v>
       </c>
       <c r="V16" t="n">
         <v>1.2594</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1264</v>
+        <v>0.2495</v>
       </c>
       <c r="E18" t="n">
         <v>0.8692</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7428</v>
+        <v>-0.6197</v>
       </c>
       <c r="G18" t="n">
         <v>0.7621</v>
@@ -1858,13 +1858,13 @@
         <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0062</v>
+        <v>0.1169</v>
       </c>
       <c r="T18" t="n">
         <v>-0.143</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1368</v>
+        <v>0.2599</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6294</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1169</v>
+        <v>0.1597</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8953</v>
+        <v>0.4152</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7783</v>
+        <v>-0.2555</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7118</v>
+        <v>0.755</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6888</v>
+        <v>-0.8809</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.023</v>
+        <v>1.6359</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5669999999999999</v>
+        <v>1.3261</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.5583</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.7678</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1448</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1219</v>
+        <v>-1.4391</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.023</v>
+        <v>0.868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2243</v>
+        <v>-0.1337</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3283</v>
+        <v>-0.5403</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5526</v>
+        <v>0.4066</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3807</v>
+        <v>0.0051</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0587</v>
+        <v>-0.6994</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4395</v>
+        <v>0.7045</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0275</v>
+        <v>-0.7118</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09810000000000001</v>
+        <v>-0.6888</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0706</v>
+        <v>-0.023</v>
       </c>
       <c r="J20" t="n">
-        <v>0.77</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6871</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7426</v>
+        <v>-0.1448</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.589</v>
+        <v>-0.1219</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1536</v>
+        <v>-0.023</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4621</v>
+        <v>0.3463</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2151</v>
+        <v>-0.1324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.247</v>
+        <v>0.4788</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.3986</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1723</v>
+        <v>-1.2585</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3786</v>
+        <v>0.8599</v>
       </c>
       <c r="G21" t="n">
-        <v>0.755</v>
+        <v>0.7507</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8809</v>
+        <v>2.0839</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6359</v>
+        <v>-1.3332</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3261</v>
+        <v>1.4928</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5583</v>
+        <v>2.1042</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7678</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.7421</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4391</v>
+        <v>-0.0203</v>
       </c>
       <c r="O21" t="n">
-        <v>0.868</v>
+        <v>-0.7219</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1117</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3706</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8444</v>
+        <v>0.7592</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1279</v>
+        <v>0.028</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2835</v>
+        <v>0.7312</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5733</v>
+        <v>0.315</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5733</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.6006</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9997</v>
+        <v>-0.2351</v>
       </c>
       <c r="F22" t="n">
-        <v>3.4337</v>
+        <v>-0.3656</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9792999999999999</v>
+        <v>0.0275</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1177</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1384</v>
+        <v>-0.0706</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2064</v>
+        <v>0.77</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7609</v>
+        <v>0.6871</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4455</v>
+        <v>0.0829</v>
       </c>
       <c r="M22" t="n">
-        <v>0.227</v>
+        <v>-0.7426</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3568</v>
+        <v>-0.589</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5839</v>
+        <v>-0.1536</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2234</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>1.063</v>
+        <v>0.2422</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.475</v>
+        <v>-0.0786</v>
       </c>
       <c r="U22" t="n">
-        <v>1.538</v>
+        <v>0.3208</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5738</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5727</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0011</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8481</v>
+        <v>-0.9777</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4544</v>
+        <v>-3.9018</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6062</v>
+        <v>2.9241</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7507</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0839</v>
+        <v>-1.1177</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3332</v>
+        <v>0.1384</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4928</v>
+        <v>-1.2064</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1042</v>
+        <v>-0.7609</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.4455</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7421</v>
+        <v>0.227</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0203</v>
+        <v>-0.3568</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7219</v>
+        <v>0.5839</v>
       </c>
       <c r="P23" t="n">
         <v>-2.2234</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7793</v>
+        <v>-3.891</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3096</v>
+        <v>0.6513</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1679</v>
+        <v>-0.3771</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4775</v>
+        <v>1.0284</v>
       </c>
       <c r="V23" t="n">
-        <v>0.315</v>
+        <v>1.5738</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.5727</v>
       </c>
       <c r="X23" t="n">
-        <v>0.315</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3361</v>
+        <v>-1.5027</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8232</v>
+        <v>-4.5294</v>
       </c>
       <c r="F24" t="n">
-        <v>3.4871</v>
+        <v>3.0268</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9372</v>
@@ -2326,13 +2326,13 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>1.0834</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6392</v>
+        <v>-0.3454</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7225</v>
+        <v>1.2622</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. PARRA JIMENEZ</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.5329</v>
+        <v>-1.6311</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3836</v>
+        <v>-1.8726</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8507</v>
+        <v>0.2415</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.0561</v>
+        <v>-2.7175</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.9532</v>
+        <v>-2.6851</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1029</v>
+        <v>-0.0324</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.8759</v>
+        <v>-1.111</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2337</v>
+        <v>-1.6929</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6422</v>
+        <v>0.5818</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1803</v>
+        <v>-1.6065</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7196</v>
+        <v>-0.9922</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.4607</v>
+        <v>-0.6143</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="R25" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8382</v>
+        <v>0.2341</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1043</v>
+        <v>-0.2608</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7339</v>
+        <v>0.4949</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3144</v>
+        <v>-0.3155</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>I. GARCIA REYES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6688</v>
+        <v>-2.3934</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.5581</v>
+        <v>-4.2049</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1106</v>
+        <v>1.8115</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.7175</v>
+        <v>-2.2963</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6851</v>
+        <v>-1.138</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0324</v>
+        <v>-1.1583</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.111</v>
+        <v>-2.6305</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.6929</v>
+        <v>-1.3876</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5818</v>
+        <v>-1.2429</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.6065</v>
+        <v>0.3342</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9922</v>
+        <v>0.2496</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.6143</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>1.4823</v>
+        <v>0.1853</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.8036</v>
+        <v>0.3476</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9463</v>
+        <v>-0.018</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1427</v>
+        <v>0.3656</v>
       </c>
       <c r="V26" t="n">
         <v>-0.63</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.3155</v>
+        <v>-0.63</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>I. GARCIA REYES</t>
+          <t>M. PARRA JIMENEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,64 +2515,64 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7221</v>
+        <v>-2.7086</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.009</v>
+        <v>-3.4608</v>
       </c>
       <c r="F27" t="n">
-        <v>1.287</v>
+        <v>0.7522</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.2963</v>
+        <v>-4.0561</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.138</v>
+        <v>-2.9532</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.1583</v>
+        <v>-1.1029</v>
       </c>
       <c r="J27" t="n">
-        <v>-2.6305</v>
+        <v>-2.8759</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.3876</v>
+        <v>-2.2337</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.2429</v>
+        <v>-0.6422</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3342</v>
+        <v>-1.1803</v>
       </c>
       <c r="N27" t="n">
-        <v>0.2496</v>
+        <v>-0.7196</v>
       </c>
       <c r="O27" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.4607</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q27" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0189</v>
+        <v>0.6625</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1779</v>
+        <v>0.0271</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1589</v>
+        <v>0.6354</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.7171</v>
+        <v>-5.064400000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-16.8592</v>
+        <v>-16.8593</v>
       </c>
       <c r="F28" t="n">
-        <v>11.142</v>
+        <v>11.795</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.4435</v>
+        <v>-7.443499999999999</v>
       </c>
       <c r="H28" t="n">
         <v>-6.9056</v>
@@ -2611,10 +2611,10 @@
         <v>-0.5375999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.5304</v>
+        <v>-1.530399999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2615999999999998</v>
+        <v>-0.2615999999999996</v>
       </c>
       <c r="L28" t="n">
         <v>-1.2688</v>
@@ -2629,7 +2629,7 @@
         <v>0.7307000000000002</v>
       </c>
       <c r="P28" t="n">
-        <v>-2.7792</v>
+        <v>-2.779199999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.8229</v>
@@ -2638,13 +2638,13 @@
         <v>12.0437</v>
       </c>
       <c r="S28" t="n">
-        <v>4.190700000000001</v>
+        <v>4.8437</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.0766</v>
+        <v>-2.0764</v>
       </c>
       <c r="U28" t="n">
-        <v>6.2673</v>
+        <v>6.9202</v>
       </c>
       <c r="V28" t="n">
         <v>0.3149000000000002</v>
